--- a/examples/SmallDrugCombo_Zhou_CellChemBio_2026/tables/data__sa_fit_heat_GR__GR50.xlsx
+++ b/examples/SmallDrugCombo_Zhou_CellChemBio_2026/tables/data__sa_fit_heat_GR__GR50.xlsx
@@ -381,23 +381,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MCF-7</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>0.0002263583668911149</v>
+          <t>CAMA-1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
       <c r="C2">
-        <v>0.1887827393547613</v>
-      </c>
-      <c r="D2">
-        <v>0.379414810939424</v>
+        <v>0.003911921376763829</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T-47D</t>
+          <t>EFM-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -405,39 +409,33 @@
           <t>Inf</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+      <c r="C3">
+        <v>0.3348047678012369</v>
       </c>
       <c r="D3">
-        <v>0.05530573917035413</v>
+        <v>0.04660071565331715</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAMA-1</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+          <t>MCF-7</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.0002263583668911149</v>
       </c>
       <c r="C4">
-        <v>0.003911921376763829</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.1887827393547613</v>
+      </c>
+      <c r="D4">
+        <v>0.379414810939424</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EFM-19</t>
+          <t>T-47D</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -445,11 +443,13 @@
           <t>Inf</t>
         </is>
       </c>
-      <c r="C5">
-        <v>0.3348047678012369</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
       <c r="D5">
-        <v>0.04660071565331715</v>
+        <v>0.05530573917035413</v>
       </c>
     </row>
   </sheetData>
@@ -477,7 +477,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MCF-7</t>
+          <t>CAMA-1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -489,7 +489,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T-47D</t>
+          <t>EFM-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -501,7 +501,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CAMA-1</t>
+          <t>MCF-7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -513,7 +513,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EFM-19</t>
+          <t>T-47D</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
